--- a/Proyecto Interno/review-food-security-paper/00_pipeline/robust/price_validation_results.xlsx
+++ b/Proyecto Interno/review-food-security-paper/00_pipeline/robust/price_validation_results.xlsx
@@ -395,7 +395,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>8.187502353415857</v>
+        <v>8.12025866908364</v>
       </c>
     </row>
     <row r="5">
@@ -425,7 +425,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>30.71294559099437</v>
+        <v>22.5140712945591</v>
       </c>
     </row>
     <row r="8">
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.1793077756361434</v>
+        <v>-0.1120640913039264</v>
       </c>
     </row>
   </sheetData>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -493,11 +493,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>011609</t>
+          <t>011716</t>
         </is>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -505,16 +505,16 @@
         </is>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="F2">
-        <v>27.26179224209144</v>
+        <v>32.11567818383972</v>
       </c>
       <c r="G2">
-        <v>27.26179224209144</v>
+        <v>32.11567818383972</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -523,11 +523,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>011716</t>
+          <t>011609</t>
         </is>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>312</v>
+        <v>104</v>
       </c>
       <c r="F3">
-        <v>26.35781606145254</v>
+        <v>27.26179224209144</v>
       </c>
       <c r="G3">
-        <v>26.35781606145254</v>
+        <v>27.26179224209144</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -574,50 +574,50 @@
         <v>25.25306120879389</v>
       </c>
       <c r="G4">
-        <v>23.20782457641349</v>
+        <v>23.24029919928241</v>
       </c>
       <c r="H4">
-        <v>2.045236632380405</v>
+        <v>2.012762009511476</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>011712</t>
+          <t>011609</t>
         </is>
       </c>
       <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BASE_lowR2</t>
+        </is>
+      </c>
+      <c r="D5">
         <v>2</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
       <c r="E5">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="F5">
-        <v>22.13269230888435</v>
+        <v>22.33282146350568</v>
       </c>
       <c r="G5">
-        <v>23.52816769084486</v>
+        <v>22.33282146350568</v>
       </c>
       <c r="H5">
-        <v>-1.395475381960509</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>011609</t>
+          <t>011716</t>
         </is>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>156</v>
+        <v>208</v>
       </c>
       <c r="F6">
-        <v>21.80510900696624</v>
+        <v>21.62606871532862</v>
       </c>
       <c r="G6">
-        <v>21.80510900696624</v>
+        <v>21.62606871532862</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -643,11 +643,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>011716</t>
+          <t>011609</t>
         </is>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7">
-        <v>208</v>
+        <v>104</v>
       </c>
       <c r="F7">
-        <v>21.62606871532862</v>
+        <v>21.54125277869652</v>
       </c>
       <c r="G7">
-        <v>21.62606871532862</v>
+        <v>21.54125277869652</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -673,61 +673,61 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>011714</t>
+          <t>011716</t>
         </is>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>D_city</t>
+          <t>BASE_lowR2</t>
         </is>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E8">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="F8">
-        <v>20.93716918946703</v>
+        <v>20.59995393906537</v>
       </c>
       <c r="G8">
-        <v>23.06124018264381</v>
+        <v>20.59995393906537</v>
       </c>
       <c r="H8">
-        <v>-2.12407099317678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>011705</t>
+          <t>011609</t>
         </is>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BASE_lowR2</t>
+          <t>D_city</t>
         </is>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E9">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="F9">
-        <v>18.40943692252298</v>
+        <v>19.62066907743091</v>
       </c>
       <c r="G9">
-        <v>18.40943692252298</v>
+        <v>16.34545377019198</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>3.275215307238938</v>
       </c>
     </row>
     <row r="10">
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -745,19 +745,19 @@
         </is>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="F10">
-        <v>17.60180122725107</v>
+        <v>18.95849346365105</v>
       </c>
       <c r="G10">
-        <v>16.58797583493958</v>
+        <v>17.28120942759778</v>
       </c>
       <c r="H10">
-        <v>1.013825392311489</v>
+        <v>1.677284036053276</v>
       </c>
     </row>
     <row r="11">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -778,46 +778,46 @@
         <v>2</v>
       </c>
       <c r="E11">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="F11">
-        <v>17.54432496546614</v>
+        <v>18.67527304013311</v>
       </c>
       <c r="G11">
-        <v>14.39036964270007</v>
+        <v>17.30676954166992</v>
       </c>
       <c r="H11">
-        <v>3.153955322766071</v>
+        <v>1.368503498463184</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>011609</t>
+          <t>011705</t>
         </is>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>D_city</t>
+          <t>BASE_lowR2</t>
         </is>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>234</v>
+        <v>52</v>
       </c>
       <c r="F12">
-        <v>17.44726841768468</v>
+        <v>18.40943692252298</v>
       </c>
       <c r="G12">
-        <v>16.71922666073483</v>
+        <v>18.40943692252298</v>
       </c>
       <c r="H12">
-        <v>0.7280417569498567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -844,20 +844,20 @@
         <v>16.29040735612449</v>
       </c>
       <c r="G13">
-        <v>16.27422212384581</v>
+        <v>16.27089971089814</v>
       </c>
       <c r="H13">
-        <v>0.01618523227868351</v>
+        <v>0.01950764522635851</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>011705</t>
+          <t>011609</t>
         </is>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -865,49 +865,49 @@
         </is>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E14">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="F14">
-        <v>14.88765680248128</v>
+        <v>15.7085478898877</v>
       </c>
       <c r="G14">
-        <v>20.59955532057404</v>
+        <v>17.0182449731691</v>
       </c>
       <c r="H14">
-        <v>-5.711898518092752</v>
+        <v>-1.309697083281407</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>011702</t>
+          <t>011716</t>
         </is>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BASE_lowR2</t>
+          <t>D_city</t>
         </is>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="F15">
-        <v>13.19025378440418</v>
+        <v>14.88841675445109</v>
       </c>
       <c r="G15">
-        <v>13.19025378440418</v>
+        <v>15.20150864962318</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>-0.3130918951720858</v>
       </c>
     </row>
     <row r="16">
@@ -921,37 +921,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>D_city</t>
+          <t>BASE_lowR2</t>
         </is>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="F16">
-        <v>10.87169817584304</v>
+        <v>13.66718893454433</v>
       </c>
       <c r="G16">
-        <v>9.864967779270646</v>
+        <v>13.66718893454433</v>
       </c>
       <c r="H16">
-        <v>1.006730396572394</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>011505</t>
+          <t>011702</t>
         </is>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>D_city</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="D17">
@@ -961,40 +961,40 @@
         <v>52</v>
       </c>
       <c r="F17">
-        <v>10.67335648744768</v>
+        <v>11.55404082998346</v>
       </c>
       <c r="G17">
-        <v>13.4725380655422</v>
+        <v>11.55404082998346</v>
       </c>
       <c r="H17">
-        <v>-2.799181578094519</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>011106</t>
+          <t>011505</t>
         </is>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BASE_lowR2</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="F18">
-        <v>9.57841414394102</v>
+        <v>10.12553690411389</v>
       </c>
       <c r="G18">
-        <v>9.57841414394102</v>
+        <v>10.12553690411389</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -1003,88 +1003,88 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>011505</t>
+          <t>011712</t>
         </is>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>D_city</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="F19">
-        <v>9.029897737446323</v>
+        <v>9.983255715717652</v>
       </c>
       <c r="G19">
-        <v>9.034791819204333</v>
+        <v>9.983255715717652</v>
       </c>
       <c r="H19">
-        <v>-0.004894081758010316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>011106</t>
+          <t>011705</t>
         </is>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BASE_lowR2</t>
+          <t>D_city</t>
         </is>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="F20">
-        <v>7.376938108419627</v>
+        <v>8.850092894540335</v>
       </c>
       <c r="G20">
-        <v>7.376938108419627</v>
+        <v>11.45358449190029</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>-2.60349159735995</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>011105</t>
+          <t>011106</t>
         </is>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BASE_lowR2</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="F21">
-        <v>7.138846263440529</v>
+        <v>8.400330071794642</v>
       </c>
       <c r="G21">
-        <v>7.138846263440529</v>
+        <v>8.400330071794642</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1093,11 +1093,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>011105</t>
+          <t>011106</t>
         </is>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1105,16 +1105,16 @@
         </is>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="F22">
-        <v>6.952643045912754</v>
+        <v>7.531630217190989</v>
       </c>
       <c r="G22">
-        <v>6.952643045912754</v>
+        <v>7.531630217190989</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -1123,7 +1123,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>011303</t>
+          <t>011105</t>
         </is>
       </c>
       <c r="B23">
@@ -1131,29 +1131,29 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>D_city</t>
+          <t>BASE_lowR2</t>
         </is>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="F23">
-        <v>6.699935862858106</v>
+        <v>7.26362064848232</v>
       </c>
       <c r="G23">
-        <v>9.042459790547156</v>
+        <v>7.26362064848232</v>
       </c>
       <c r="H23">
-        <v>-2.34252392768905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>011303</t>
+          <t>011105</t>
         </is>
       </c>
       <c r="B24">
@@ -1168,13 +1168,13 @@
         <v>2</v>
       </c>
       <c r="E24">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="F24">
-        <v>5.623160196578893</v>
+        <v>6.807392383375634</v>
       </c>
       <c r="G24">
-        <v>5.623160196578893</v>
+        <v>6.807392383375634</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -1183,91 +1183,91 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>011201</t>
+          <t>011303</t>
         </is>
       </c>
       <c r="B25">
+        <v>5</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>D_city</t>
+        </is>
+      </c>
+      <c r="D25">
         <v>3</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>BASE_lowR2</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
       <c r="E25">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="F25">
-        <v>5.24719104476269</v>
+        <v>5.791688887021465</v>
       </c>
       <c r="G25">
-        <v>5.24719104476269</v>
+        <v>7.449834431748157</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>-1.658145544726692</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>011303</t>
+          <t>011201</t>
         </is>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>D_city</t>
+          <t>BASE_lowR2</t>
         </is>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="F26">
-        <v>3.975194935348183</v>
+        <v>5.24719104476269</v>
       </c>
       <c r="G26">
-        <v>4.263146496425734</v>
+        <v>5.24719104476269</v>
       </c>
       <c r="H26">
-        <v>-0.2879515610775516</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>011712</t>
+          <t>011303</t>
         </is>
       </c>
       <c r="B27">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BASE_lowR2</t>
+        </is>
+      </c>
+      <c r="D27">
         <v>3</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
       <c r="E27">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="F27">
-        <v>3.908537419134302</v>
+        <v>3.897994533310528</v>
       </c>
       <c r="G27">
-        <v>1.639139485952473</v>
+        <v>3.897994533310528</v>
       </c>
       <c r="H27">
-        <v>2.269397933181829</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1294,16 +1294,16 @@
         <v>3.884282091569759</v>
       </c>
       <c r="G28">
-        <v>3.209426594272017</v>
+        <v>3.230218461405679</v>
       </c>
       <c r="H28">
-        <v>0.6748554972977425</v>
+        <v>0.6540636301640803</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>011103</t>
+          <t>011201</t>
         </is>
       </c>
       <c r="B29">
@@ -1321,23 +1321,23 @@
         <v>104</v>
       </c>
       <c r="F29">
-        <v>3.579383085138834</v>
+        <v>3.271006162829896</v>
       </c>
       <c r="G29">
-        <v>2.143560092877498</v>
+        <v>5.272799282460538</v>
       </c>
       <c r="H29">
-        <v>1.435822992261337</v>
+        <v>-2.001793119630642</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>011201</t>
+          <t>011103</t>
         </is>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1348,22 +1348,22 @@
         <v>2</v>
       </c>
       <c r="E30">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="F30">
-        <v>3.271006162829896</v>
+        <v>3.110780528594438</v>
       </c>
       <c r="G30">
-        <v>5.281703651871618</v>
+        <v>2.153255805554372</v>
       </c>
       <c r="H30">
-        <v>-2.010697489041723</v>
+        <v>0.9575247230400654</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>011401</t>
+          <t>011501</t>
         </is>
       </c>
       <c r="B31">
@@ -1378,16 +1378,16 @@
         <v>2</v>
       </c>
       <c r="E31">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="F31">
-        <v>3.191564924344024</v>
+        <v>2.537033879219202</v>
       </c>
       <c r="G31">
-        <v>2.264548717602866</v>
+        <v>2.144211507565659</v>
       </c>
       <c r="H31">
-        <v>0.927016206741158</v>
+        <v>0.3928223716535424</v>
       </c>
     </row>
     <row r="32">
@@ -1397,24 +1397,24 @@
         </is>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BASE_fallback</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
       <c r="E32">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="F32">
-        <v>3.174840719927952</v>
+        <v>2.426746183396388</v>
       </c>
       <c r="G32">
-        <v>3.174840719927952</v>
+        <v>2.426746183396388</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -1423,7 +1423,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>011501</t>
+          <t>011201</t>
         </is>
       </c>
       <c r="B33">
@@ -1441,53 +1441,53 @@
         <v>52</v>
       </c>
       <c r="F33">
-        <v>3.156235390001496</v>
+        <v>2.16877099092987</v>
       </c>
       <c r="G33">
-        <v>2.997885310495508</v>
+        <v>4.188283676016777</v>
       </c>
       <c r="H33">
-        <v>0.1583500795059885</v>
+        <v>-2.019512685086907</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>011402</t>
+          <t>011401</t>
         </is>
       </c>
       <c r="B34">
+        <v>4</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>D_city</t>
+        </is>
+      </c>
+      <c r="D34">
         <v>2</v>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
       <c r="E34">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="F34">
-        <v>3.040712230700749</v>
+        <v>2.017833452377325</v>
       </c>
       <c r="G34">
-        <v>6.574279444790668</v>
+        <v>1.836735198737431</v>
       </c>
       <c r="H34">
-        <v>-3.533567214089919</v>
+        <v>0.181098253639894</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>011303</t>
+          <t>011401</t>
         </is>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1495,16 +1495,16 @@
         </is>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="F35">
-        <v>3.035411701676346</v>
+        <v>1.946749518998838</v>
       </c>
       <c r="G35">
-        <v>3.035411701676346</v>
+        <v>1.946749518998838</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -1513,11 +1513,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>011705</t>
+          <t>011203</t>
         </is>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1525,29 +1525,29 @@
         </is>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="F36">
-        <v>2.812528986599384</v>
+        <v>1.784859786011916</v>
       </c>
       <c r="G36">
-        <v>2.415877798718927</v>
+        <v>2.100274094728163</v>
       </c>
       <c r="H36">
-        <v>0.3966511878804568</v>
+        <v>-0.3154143087162473</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>011203</t>
+          <t>011108</t>
         </is>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1555,25 +1555,25 @@
         </is>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37">
-        <v>52</v>
+        <v>234</v>
       </c>
       <c r="F37">
-        <v>2.743077302987541</v>
+        <v>1.774711224409691</v>
       </c>
       <c r="G37">
-        <v>2.992328548077321</v>
+        <v>2.797260316283478</v>
       </c>
       <c r="H37">
-        <v>-0.2492512450897801</v>
+        <v>-1.022549091873787</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>011401</t>
+          <t>011704</t>
         </is>
       </c>
       <c r="B38">
@@ -1581,33 +1581,33 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BASE_lowR2</t>
+          <t>D_city</t>
         </is>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="F38">
-        <v>2.424817992825521</v>
+        <v>1.649998610459949</v>
       </c>
       <c r="G38">
-        <v>2.424817992825521</v>
+        <v>1.649997637713811</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>9.727461376396462E-07</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>011501</t>
+          <t>011101</t>
         </is>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1618,116 +1618,116 @@
         <v>2</v>
       </c>
       <c r="E39">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="F39">
-        <v>2.227433123828054</v>
+        <v>1.566429560710012</v>
       </c>
       <c r="G39">
-        <v>1.714609919913682</v>
+        <v>1.141579520474608</v>
       </c>
       <c r="H39">
-        <v>0.5128232039143719</v>
+        <v>0.4248500402354038</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>011103</t>
+          <t>011402</t>
         </is>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>D_city</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="F40">
-        <v>2.173575415505645</v>
+        <v>1.480498299356599</v>
       </c>
       <c r="G40">
-        <v>2.19130589380643</v>
+        <v>1.480498299356599</v>
       </c>
       <c r="H40">
-        <v>-0.01773047830078589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>011201</t>
+          <t>011802</t>
         </is>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>D_city</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="F41">
-        <v>2.16877099092987</v>
+        <v>1.470423681371154</v>
       </c>
       <c r="G41">
-        <v>4.188283676016777</v>
+        <v>1.470423681371154</v>
       </c>
       <c r="H41">
-        <v>-2.019512685086907</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>011108</t>
+          <t>011608</t>
         </is>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>D_city</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E42">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="F42">
-        <v>2.066598006089192</v>
+        <v>1.470013648004185</v>
       </c>
       <c r="G42">
-        <v>3.398026284884138</v>
+        <v>1.470013648004185</v>
       </c>
       <c r="H42">
-        <v>-1.331428278794946</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>011802</t>
+          <t>011202</t>
         </is>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1735,19 +1735,19 @@
         </is>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="F43">
-        <v>2.032805840844849</v>
+        <v>1.397420645684947</v>
       </c>
       <c r="G43">
-        <v>2.684521526710272</v>
+        <v>2.354537478298113</v>
       </c>
       <c r="H43">
-        <v>-0.6517156858654229</v>
+        <v>-0.9571168326131665</v>
       </c>
     </row>
     <row r="44">
@@ -1768,26 +1768,26 @@
         <v>2</v>
       </c>
       <c r="E44">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="F44">
-        <v>1.968370283509542</v>
+        <v>1.372949582430133</v>
       </c>
       <c r="G44">
-        <v>1.925242488010071</v>
+        <v>1.293391034405007</v>
       </c>
       <c r="H44">
-        <v>0.04312779549947043</v>
+        <v>0.07955854802512552</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>011608</t>
+          <t>011703</t>
         </is>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1795,25 +1795,25 @@
         </is>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="F45">
-        <v>1.852779152337072</v>
+        <v>1.365294536043649</v>
       </c>
       <c r="G45">
-        <v>1.89744742235453</v>
+        <v>2.296753711714921</v>
       </c>
       <c r="H45">
-        <v>-0.04466827001745788</v>
+        <v>-0.9314591756712716</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>011401</t>
+          <t>011202</t>
         </is>
       </c>
       <c r="B46">
@@ -1821,29 +1821,29 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BASE_lowR2</t>
+          <t>D_city</t>
         </is>
       </c>
       <c r="D46">
         <v>2</v>
       </c>
       <c r="E46">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="F46">
-        <v>1.707715282085496</v>
+        <v>1.223497814595238</v>
       </c>
       <c r="G46">
-        <v>1.707715282085496</v>
+        <v>2.43549024128975</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>-1.211992426694511</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>011101</t>
+          <t>011801</t>
         </is>
       </c>
       <c r="B47">
@@ -1858,976 +1858,286 @@
         <v>2</v>
       </c>
       <c r="E47">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="F47">
-        <v>1.566429560710012</v>
+        <v>0.9939985260009598</v>
       </c>
       <c r="G47">
-        <v>1.141579520474608</v>
+        <v>1.212194267108604</v>
       </c>
       <c r="H47">
-        <v>0.4248500402354038</v>
+        <v>-0.2181957411076443</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>011401</t>
+          <t>011605</t>
         </is>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>D_city</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="F48">
-        <v>1.430967716393976</v>
+        <v>0.9298944669808493</v>
       </c>
       <c r="G48">
-        <v>1.632582653828365</v>
+        <v>0.9298944669808493</v>
       </c>
       <c r="H48">
-        <v>-0.2016149374343887</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>011703</t>
+          <t>011405</t>
         </is>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>D_city</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="F49">
-        <v>1.404161790685203</v>
+        <v>0.9157350100027085</v>
       </c>
       <c r="G49">
-        <v>3.006495238528046</v>
+        <v>0.9157350100027085</v>
       </c>
       <c r="H49">
-        <v>-1.602333447842843</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>011202</t>
+          <t>011607</t>
         </is>
       </c>
       <c r="B50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>D_city</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="F50">
-        <v>1.403306540034728</v>
+        <v>0.8663081986608547</v>
       </c>
       <c r="G50">
-        <v>2.619565648344516</v>
+        <v>0.8663081986608547</v>
       </c>
       <c r="H50">
-        <v>-1.216259108309788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>011203</t>
+          <t>011715</t>
         </is>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>D_city</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="F51">
-        <v>1.305751027524103</v>
+        <v>0.7567380385134328</v>
       </c>
       <c r="G51">
-        <v>1.652422546709003</v>
+        <v>0.7567380385134328</v>
       </c>
       <c r="H51">
-        <v>-0.3466715191848999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>011703</t>
+          <t>011713</t>
         </is>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>D_city</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="F52">
-        <v>1.287560026760541</v>
+        <v>0.6798510090700105</v>
       </c>
       <c r="G52">
-        <v>0.8865867837082807</v>
+        <v>0.6798510090700105</v>
       </c>
       <c r="H52">
-        <v>0.4009732430522605</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>011801</t>
+          <t>011606</t>
         </is>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>D_city</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="F53">
-        <v>1.253707476551283</v>
+        <v>0.5384004335681463</v>
       </c>
       <c r="G53">
-        <v>1.58630102641129</v>
+        <v>0.5384004335681463</v>
       </c>
       <c r="H53">
-        <v>-0.332593549860007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>011405</t>
+          <t>011704</t>
         </is>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>D_city</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="D54">
         <v>1</v>
       </c>
       <c r="E54">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="F54">
-        <v>1.2258078040987</v>
+        <v>0.5143043673973182</v>
       </c>
       <c r="G54">
-        <v>1.267438136483056</v>
+        <v>0.5143043673973182</v>
       </c>
       <c r="H54">
-        <v>-0.04163033238435609</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>011202</t>
+          <t>011706</t>
         </is>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>D_city</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="F55">
-        <v>1.211726025895675</v>
+        <v>0.4608833177198204</v>
       </c>
       <c r="G55">
-        <v>1.915890193483896</v>
+        <v>0.4608833177198204</v>
       </c>
       <c r="H55">
-        <v>-0.7041641675882213</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>011108</t>
+          <t>011902</t>
         </is>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>D_city</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="D56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E56">
         <v>78</v>
       </c>
       <c r="F56">
-        <v>1.19093766105069</v>
+        <v>0.3734976553058197</v>
       </c>
       <c r="G56">
-        <v>1.575820431832694</v>
+        <v>0.3734976553058197</v>
       </c>
       <c r="H56">
-        <v>-0.3848827707820042</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>011607</t>
-        </is>
-      </c>
-      <c r="B57">
-        <v>3</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D57">
-        <v>1</v>
-      </c>
-      <c r="E57">
-        <v>52</v>
-      </c>
-      <c r="F57">
-        <v>1.156422855733125</v>
-      </c>
-      <c r="G57">
-        <v>1.041626358229244</v>
-      </c>
-      <c r="H57">
-        <v>0.1147964975038813</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>011102</t>
-        </is>
-      </c>
-      <c r="B58">
-        <v>3</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D58">
-        <v>2</v>
-      </c>
-      <c r="E58">
-        <v>104</v>
-      </c>
-      <c r="F58">
-        <v>1.075239231890428</v>
-      </c>
-      <c r="G58">
-        <v>0.9775054903594917</v>
-      </c>
-      <c r="H58">
-        <v>0.09773374153093672</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>011605</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>3</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D59">
-        <v>1</v>
-      </c>
-      <c r="E59">
-        <v>52</v>
-      </c>
-      <c r="F59">
-        <v>1.012141217872604</v>
-      </c>
-      <c r="G59">
-        <v>1.058940024397159</v>
-      </c>
-      <c r="H59">
-        <v>-0.04679880652455504</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>011704</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>3</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D60">
-        <v>1</v>
-      </c>
-      <c r="E60">
-        <v>52</v>
-      </c>
-      <c r="F60">
-        <v>0.9624928033072696</v>
-      </c>
-      <c r="G60">
-        <v>1.068983099432111</v>
-      </c>
-      <c r="H60">
-        <v>-0.1064902961248414</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>012101</t>
-        </is>
-      </c>
-      <c r="B61">
-        <v>2</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>BASE_fallback</t>
-        </is>
-      </c>
-      <c r="D61">
-        <v>1</v>
-      </c>
-      <c r="E61">
-        <v>26</v>
-      </c>
-      <c r="F61">
-        <v>0.9305571103332612</v>
-      </c>
-      <c r="G61">
-        <v>0.9305571103332612</v>
-      </c>
-      <c r="H61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>011713</t>
-        </is>
-      </c>
-      <c r="B62">
-        <v>3</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D62">
-        <v>1</v>
-      </c>
-      <c r="E62">
-        <v>52</v>
-      </c>
-      <c r="F62">
-        <v>0.8179222276702788</v>
-      </c>
-      <c r="G62">
-        <v>0.8428991250127008</v>
-      </c>
-      <c r="H62">
-        <v>-0.02497689734242203</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>011715</t>
-        </is>
-      </c>
-      <c r="B63">
-        <v>3</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D63">
-        <v>1</v>
-      </c>
-      <c r="E63">
-        <v>52</v>
-      </c>
-      <c r="F63">
-        <v>0.8029334415706517</v>
-      </c>
-      <c r="G63">
-        <v>0.8960896045008367</v>
-      </c>
-      <c r="H63">
-        <v>-0.09315616293018503</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>011605</t>
-        </is>
-      </c>
-      <c r="B64">
-        <v>2</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-      <c r="E64">
-        <v>26</v>
-      </c>
-      <c r="F64">
-        <v>0.7654009651973397</v>
-      </c>
-      <c r="G64">
-        <v>0.5535647783812121</v>
-      </c>
-      <c r="H64">
-        <v>0.2118361868161276</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>011405</t>
-        </is>
-      </c>
-      <c r="B65">
-        <v>3</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D65">
-        <v>1</v>
-      </c>
-      <c r="E65">
-        <v>52</v>
-      </c>
-      <c r="F65">
-        <v>0.7606986129547125</v>
-      </c>
-      <c r="G65">
-        <v>0.8853062924165467</v>
-      </c>
-      <c r="H65">
-        <v>-0.1246076794618342</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>011704</t>
-        </is>
-      </c>
-      <c r="B66">
-        <v>2</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D66">
-        <v>1</v>
-      </c>
-      <c r="E66">
-        <v>26</v>
-      </c>
-      <c r="F66">
-        <v>0.753621738640046</v>
-      </c>
-      <c r="G66">
-        <v>0.9096451793824011</v>
-      </c>
-      <c r="H66">
-        <v>-0.1560234407423551</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>011608</t>
-        </is>
-      </c>
-      <c r="B67">
-        <v>2</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D67">
-        <v>1</v>
-      </c>
-      <c r="E67">
-        <v>26</v>
-      </c>
-      <c r="F67">
-        <v>0.7044826393384088</v>
-      </c>
-      <c r="G67">
-        <v>0.698364734435567</v>
-      </c>
-      <c r="H67">
-        <v>0.006117904902841809</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>011402</t>
-        </is>
-      </c>
-      <c r="B68">
-        <v>3</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D68">
-        <v>1</v>
-      </c>
-      <c r="E68">
-        <v>52</v>
-      </c>
-      <c r="F68">
-        <v>0.7003913336845233</v>
-      </c>
-      <c r="G68">
-        <v>3.757065583542266</v>
-      </c>
-      <c r="H68">
-        <v>-3.056674249857743</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>011715</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>2</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D69">
-        <v>1</v>
-      </c>
-      <c r="E69">
-        <v>26</v>
-      </c>
-      <c r="F69">
-        <v>0.6643472323989948</v>
-      </c>
-      <c r="G69">
-        <v>0.6264604665154013</v>
-      </c>
-      <c r="H69">
-        <v>0.03788676588359352</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>011606</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>3</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D70">
-        <v>1</v>
-      </c>
-      <c r="E70">
-        <v>52</v>
-      </c>
-      <c r="F70">
-        <v>0.6323491119846654</v>
-      </c>
-      <c r="G70">
-        <v>0.512735000793862</v>
-      </c>
-      <c r="H70">
-        <v>0.1196141111908033</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>011706</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>3</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D71">
-        <v>1</v>
-      </c>
-      <c r="E71">
-        <v>52</v>
-      </c>
-      <c r="F71">
-        <v>0.5639348005838539</v>
-      </c>
-      <c r="G71">
-        <v>0.8386786876785292</v>
-      </c>
-      <c r="H71">
-        <v>-0.2747438870946752</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>011902</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>2</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D72">
-        <v>1</v>
-      </c>
-      <c r="E72">
-        <v>26</v>
-      </c>
-      <c r="F72">
-        <v>0.4840547651189584</v>
-      </c>
-      <c r="G72">
-        <v>0.3297440349122036</v>
-      </c>
-      <c r="H72">
-        <v>0.1543107302067548</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>011801</t>
-        </is>
-      </c>
-      <c r="B73">
-        <v>2</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D73">
-        <v>2</v>
-      </c>
-      <c r="E73">
-        <v>52</v>
-      </c>
-      <c r="F73">
-        <v>0.4745806249003138</v>
-      </c>
-      <c r="G73">
-        <v>0.4885783865996676</v>
-      </c>
-      <c r="H73">
-        <v>-0.01399776169935379</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>011713</t>
-        </is>
-      </c>
-      <c r="B74">
-        <v>2</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D74">
-        <v>1</v>
-      </c>
-      <c r="E74">
-        <v>26</v>
-      </c>
-      <c r="F74">
-        <v>0.4037085718694741</v>
-      </c>
-      <c r="G74">
-        <v>0.4000015875188488</v>
-      </c>
-      <c r="H74">
-        <v>0.003706984350625275</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>011606</t>
-        </is>
-      </c>
-      <c r="B75">
-        <v>2</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D75">
-        <v>1</v>
-      </c>
-      <c r="E75">
-        <v>26</v>
-      </c>
-      <c r="F75">
-        <v>0.350503076735108</v>
-      </c>
-      <c r="G75">
-        <v>0.9732302988303007</v>
-      </c>
-      <c r="H75">
-        <v>-0.6227272220951927</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>011802</t>
-        </is>
-      </c>
-      <c r="B76">
-        <v>2</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D76">
-        <v>1</v>
-      </c>
-      <c r="E76">
-        <v>26</v>
-      </c>
-      <c r="F76">
-        <v>0.3456593624237623</v>
-      </c>
-      <c r="G76">
-        <v>0.2506479808730535</v>
-      </c>
-      <c r="H76">
-        <v>0.09501138155070882</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>011902</t>
-        </is>
-      </c>
-      <c r="B77">
-        <v>3</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D77">
-        <v>1</v>
-      </c>
-      <c r="E77">
-        <v>52</v>
-      </c>
-      <c r="F77">
-        <v>0.3182191003992504</v>
-      </c>
-      <c r="G77">
-        <v>0.3459088250028324</v>
-      </c>
-      <c r="H77">
-        <v>-0.02768972460358204</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>011607</t>
-        </is>
-      </c>
-      <c r="B78">
-        <v>2</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D78">
-        <v>1</v>
-      </c>
-      <c r="E78">
-        <v>26</v>
-      </c>
-      <c r="F78">
-        <v>0.2860788845163144</v>
-      </c>
-      <c r="G78">
-        <v>0.2824642167447321</v>
-      </c>
-      <c r="H78">
-        <v>0.003614667771582314</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>011706</t>
-        </is>
-      </c>
-      <c r="B79">
-        <v>2</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="D79">
-        <v>1</v>
-      </c>
-      <c r="E79">
-        <v>26</v>
-      </c>
-      <c r="F79">
-        <v>0.2547803519917533</v>
-      </c>
-      <c r="G79">
-        <v>0.2542187727406757</v>
-      </c>
-      <c r="H79">
-        <v>0.0005615792510776374</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2909,7 +2219,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2949,7 +2259,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2989,7 +2299,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3029,7 +2339,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -3069,7 +2379,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -3109,7 +2419,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3149,7 +2459,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -3189,7 +2499,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -3229,7 +2539,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -3269,7 +2579,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -3389,7 +2699,7 @@
         </is>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3406,10 +2716,10 @@
         <v>25.25306120879389</v>
       </c>
       <c r="I14">
-        <v>23.20782457641349</v>
+        <v>23.24029919928241</v>
       </c>
       <c r="J14">
-        <v>2.045236632380405</v>
+        <v>2.012762009511476</v>
       </c>
     </row>
     <row r="15">
@@ -3429,7 +2739,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -3469,7 +2779,7 @@
         </is>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3509,7 +2819,7 @@
         </is>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -3526,10 +2836,10 @@
         <v>23.77352782977989</v>
       </c>
       <c r="I17">
-        <v>24.20449395237175</v>
+        <v>24.14713231541209</v>
       </c>
       <c r="J17">
-        <v>-0.4309661225918582</v>
+        <v>-0.3736044856321996</v>
       </c>
     </row>
     <row r="18">
@@ -3549,7 +2859,7 @@
         </is>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -3589,7 +2899,7 @@
         </is>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -3629,15 +2939,12 @@
         </is>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F20">
-        <v>0.7028334736018181</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G20">
         <v>26</v>
@@ -3646,10 +2953,10 @@
         <v>22.13269230888435</v>
       </c>
       <c r="I20">
-        <v>23.52816769084486</v>
+        <v>22.13269230888435</v>
       </c>
       <c r="J20">
-        <v>-1.395475381960509</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3669,7 +2976,7 @@
         </is>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -3686,10 +2993,10 @@
         <v>21.87545167429152</v>
       </c>
       <c r="I21">
-        <v>22.69220678924466</v>
+        <v>22.76832921015395</v>
       </c>
       <c r="J21">
-        <v>-0.8167551149531462</v>
+        <v>-0.8928775358624321</v>
       </c>
     </row>
     <row r="22">
@@ -3709,7 +3016,7 @@
         </is>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -3749,7 +3056,7 @@
         </is>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -3789,7 +3096,7 @@
         </is>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -3829,7 +3136,7 @@
         </is>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -3846,10 +3153,10 @@
         <v>21.09646787995646</v>
       </c>
       <c r="I25">
-        <v>21.08082010433314</v>
+        <v>20.97631997844799</v>
       </c>
       <c r="J25">
-        <v>0.01564777562331798</v>
+        <v>0.1201479015084708</v>
       </c>
     </row>
     <row r="26">
@@ -3869,7 +3176,7 @@
         </is>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -3909,7 +3216,7 @@
         </is>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -3949,7 +3256,7 @@
         </is>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -3989,7 +3296,7 @@
         </is>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -4029,7 +3336,7 @@
         </is>
       </c>
       <c r="D30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -4046,10 +3353,10 @@
         <v>18.64839837683415</v>
       </c>
       <c r="I30">
-        <v>9.416494474119126</v>
+        <v>9.585789416812498</v>
       </c>
       <c r="J30">
-        <v>9.231903902715025</v>
+        <v>9.062608960021654</v>
       </c>
     </row>
     <row r="31">
@@ -4069,7 +3376,7 @@
         </is>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -4109,7 +3416,7 @@
         </is>
       </c>
       <c r="D32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -4149,7 +3456,7 @@
         </is>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -4189,7 +3496,7 @@
         </is>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -4229,7 +3536,7 @@
         </is>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -4246,10 +3553,10 @@
         <v>15.09840870088365</v>
       </c>
       <c r="I35">
-        <v>12.92750872731476</v>
+        <v>12.95205431513802</v>
       </c>
       <c r="J35">
-        <v>2.170899973568895</v>
+        <v>2.146354385745632</v>
       </c>
     </row>
     <row r="36">
@@ -4269,7 +3576,7 @@
         </is>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -4309,7 +3616,7 @@
         </is>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -4349,7 +3656,7 @@
         </is>
       </c>
       <c r="D38">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -4389,7 +3696,7 @@
         </is>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -4469,7 +3776,7 @@
         </is>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -4509,7 +3816,7 @@
         </is>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -4549,7 +3856,7 @@
         </is>
       </c>
       <c r="D43">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -4589,7 +3896,7 @@
         </is>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -4629,15 +3936,12 @@
         </is>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F45">
-        <v>0.2992039831349398</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G45">
         <v>26</v>
@@ -4646,10 +3950,10 @@
         <v>12.90928863696114</v>
       </c>
       <c r="I45">
-        <v>14.70103376114237</v>
+        <v>12.90928863696114</v>
       </c>
       <c r="J45">
-        <v>-1.791745124181235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4669,7 +3973,7 @@
         </is>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -4686,10 +3990,10 @@
         <v>12.65696495436686</v>
       </c>
       <c r="I46">
-        <v>11.01298141699463</v>
+        <v>11.0331608373693</v>
       </c>
       <c r="J46">
-        <v>1.643983537372227</v>
+        <v>1.623804116997565</v>
       </c>
     </row>
     <row r="47">
@@ -4709,7 +4013,7 @@
         </is>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -4749,7 +4053,7 @@
         </is>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -4789,15 +4093,12 @@
         </is>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>BASE_lowR2</t>
-        </is>
-      </c>
-      <c r="F49">
-        <v>0.00703446298804782</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G49">
         <v>26</v>
@@ -4829,7 +4130,7 @@
         </is>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -4846,10 +4147,10 @@
         <v>11.95570962177434</v>
       </c>
       <c r="I50">
-        <v>13.15013112282319</v>
+        <v>13.16685887576927</v>
       </c>
       <c r="J50">
-        <v>-1.194421501048856</v>
+        <v>-1.211149253994929</v>
       </c>
     </row>
     <row r="51">
@@ -4869,7 +4170,7 @@
         </is>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -4909,7 +4210,7 @@
         </is>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -4949,15 +4250,12 @@
         </is>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F53">
-        <v>0.2169028125338024</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G53">
         <v>26</v>
@@ -4966,10 +4264,10 @@
         <v>10.87169817584304</v>
       </c>
       <c r="I53">
-        <v>9.864967779270646</v>
+        <v>10.87169817584304</v>
       </c>
       <c r="J53">
-        <v>1.006730396572394</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4989,7 +4287,7 @@
         </is>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -5029,7 +4327,7 @@
         </is>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -5046,10 +4344,10 @@
         <v>10.23400024847566</v>
       </c>
       <c r="I55">
-        <v>8.173730478982243</v>
+        <v>8.172090779221334</v>
       </c>
       <c r="J55">
-        <v>2.060269769493422</v>
+        <v>2.061909469254331</v>
       </c>
     </row>
     <row r="56">
@@ -5069,7 +4367,7 @@
         </is>
       </c>
       <c r="D56">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -5109,7 +4407,7 @@
         </is>
       </c>
       <c r="D57">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -5149,15 +4447,12 @@
         </is>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>BASE_lowR2</t>
-        </is>
-      </c>
-      <c r="F58">
-        <v>0.02833415320688069</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G58">
         <v>26</v>
@@ -5189,7 +4484,7 @@
         </is>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -5229,15 +4524,12 @@
         </is>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F60">
-        <v>0.6701158361631258</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G60">
         <v>26</v>
@@ -5246,10 +4538,10 @@
         <v>9.029897737446323</v>
       </c>
       <c r="I60">
-        <v>9.034791819204333</v>
+        <v>9.029897737446323</v>
       </c>
       <c r="J60">
-        <v>-0.004894081758010316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -5269,7 +4561,7 @@
         </is>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -5309,7 +4601,7 @@
         </is>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -5349,15 +4641,12 @@
         </is>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F63">
-        <v>0.2373174737376899</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G63">
         <v>26</v>
@@ -5366,10 +4655,10 @@
         <v>8.437424337934214</v>
       </c>
       <c r="I63">
-        <v>12.24404236994202</v>
+        <v>8.437424337934214</v>
       </c>
       <c r="J63">
-        <v>-3.806618032007803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -5389,7 +4678,7 @@
         </is>
       </c>
       <c r="D64">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -5469,7 +4758,7 @@
         </is>
       </c>
       <c r="D66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -5549,7 +4838,7 @@
         </is>
       </c>
       <c r="D68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -5589,7 +4878,7 @@
         </is>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -5629,7 +4918,7 @@
         </is>
       </c>
       <c r="D70">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -5669,15 +4958,12 @@
         </is>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>BASE_lowR2</t>
-        </is>
-      </c>
-      <c r="F71">
-        <v>0.04087706015905377</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G71">
         <v>26</v>
@@ -5709,15 +4995,12 @@
         </is>
       </c>
       <c r="D72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F72">
-        <v>0.9093297824951428</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G72">
         <v>26</v>
@@ -5726,10 +5009,10 @@
         <v>7.14502634276839</v>
       </c>
       <c r="I72">
-        <v>2.549051654444607</v>
+        <v>7.14502634276839</v>
       </c>
       <c r="J72">
-        <v>4.595974688323783</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -5806,10 +5089,10 @@
         <v>7.115052082367281</v>
       </c>
       <c r="I74">
-        <v>6.395479774917047</v>
+        <v>6.405311894865028</v>
       </c>
       <c r="J74">
-        <v>0.7195723074502345</v>
+        <v>0.7097401875022538</v>
       </c>
     </row>
     <row r="75">
@@ -5869,7 +5152,7 @@
         </is>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -5909,7 +5192,7 @@
         </is>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -5989,7 +5272,7 @@
         </is>
       </c>
       <c r="D79">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -6046,10 +5329,10 @@
         <v>5.695300686470406</v>
       </c>
       <c r="I80">
-        <v>8.606430296262488</v>
+        <v>8.587409426668444</v>
       </c>
       <c r="J80">
-        <v>-2.911129609792082</v>
+        <v>-2.892108740198037</v>
       </c>
     </row>
     <row r="81">
@@ -6069,7 +5352,7 @@
         </is>
       </c>
       <c r="D81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -6189,7 +5472,7 @@
         </is>
       </c>
       <c r="D84">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -6269,7 +5552,7 @@
         </is>
       </c>
       <c r="D86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -6286,10 +5569,10 @@
         <v>4.890360866036514</v>
       </c>
       <c r="I86">
-        <v>0.6619867785766633</v>
+        <v>0.662566345090442</v>
       </c>
       <c r="J86">
-        <v>4.228374087459851</v>
+        <v>4.227794520946071</v>
       </c>
     </row>
     <row r="87">
@@ -6309,7 +5592,7 @@
         </is>
       </c>
       <c r="D87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -6326,10 +5609,10 @@
         <v>4.238038927113688</v>
       </c>
       <c r="I87">
-        <v>2.506012876859462</v>
+        <v>2.522545634662751</v>
       </c>
       <c r="J87">
-        <v>1.732026050254226</v>
+        <v>1.715493292450937</v>
       </c>
     </row>
     <row r="88">
@@ -6349,7 +5632,7 @@
         </is>
       </c>
       <c r="D88">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -6366,10 +5649,10 @@
         <v>4.235891043453122</v>
       </c>
       <c r="I88">
-        <v>4.881921140977125</v>
+        <v>4.88361418900595</v>
       </c>
       <c r="J88">
-        <v>-0.6460300975240036</v>
+        <v>-0.6477231455528285</v>
       </c>
     </row>
     <row r="89">
@@ -6389,7 +5672,7 @@
         </is>
       </c>
       <c r="D89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -6406,10 +5689,10 @@
         <v>4.222730116331245</v>
       </c>
       <c r="I89">
-        <v>2.823546793494315</v>
+        <v>2.839654191416223</v>
       </c>
       <c r="J89">
-        <v>1.39918332283693</v>
+        <v>1.383075924915023</v>
       </c>
     </row>
     <row r="90">
@@ -6469,7 +5752,7 @@
         </is>
       </c>
       <c r="D91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -6486,10 +5769,10 @@
         <v>3.990275610474871</v>
       </c>
       <c r="I91">
-        <v>3.179189568827182</v>
+        <v>3.185019879629297</v>
       </c>
       <c r="J91">
-        <v>0.8110860416476893</v>
+        <v>0.8052557308455746</v>
       </c>
     </row>
     <row r="92">
@@ -6509,7 +5792,7 @@
         </is>
       </c>
       <c r="D92">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -6589,11 +5872,11 @@
         </is>
       </c>
       <c r="D94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>BASE_fallback</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="G94">
@@ -6626,7 +5909,7 @@
         </is>
       </c>
       <c r="D95">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -6643,10 +5926,10 @@
         <v>3.714498827243244</v>
       </c>
       <c r="I95">
-        <v>3.644371851874344</v>
+        <v>3.645553239294368</v>
       </c>
       <c r="J95">
-        <v>0.0701269753689</v>
+        <v>0.06894558794887518</v>
       </c>
     </row>
     <row r="96">
@@ -6666,7 +5949,7 @@
         </is>
       </c>
       <c r="D96">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -6683,10 +5966,10 @@
         <v>3.516816288621376</v>
       </c>
       <c r="I96">
-        <v>3.495130634578053</v>
+        <v>3.457641166120853</v>
       </c>
       <c r="J96">
-        <v>0.02168565404332279</v>
+        <v>0.05917512250052326</v>
       </c>
     </row>
     <row r="97">
@@ -6786,7 +6069,7 @@
         </is>
       </c>
       <c r="D99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -6803,10 +6086,10 @@
         <v>3.29380418523227</v>
       </c>
       <c r="I99">
-        <v>3.344223853187126</v>
+        <v>3.304963235423862</v>
       </c>
       <c r="J99">
-        <v>-0.05041966795485564</v>
+        <v>-0.01115905019159147</v>
       </c>
     </row>
     <row r="100">
@@ -6826,7 +6109,7 @@
         </is>
       </c>
       <c r="D100">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -6866,7 +6149,7 @@
         </is>
       </c>
       <c r="D101">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -6906,7 +6189,7 @@
         </is>
       </c>
       <c r="D102">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -6946,15 +6229,12 @@
         </is>
       </c>
       <c r="D103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F103">
-        <v>0.6376374658064468</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G103">
         <v>26</v>
@@ -6963,10 +6243,10 @@
         <v>3.040712230700749</v>
       </c>
       <c r="I103">
-        <v>6.574279444790668</v>
+        <v>3.040712230700749</v>
       </c>
       <c r="J103">
-        <v>-3.533567214089919</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -6986,7 +6266,7 @@
         </is>
       </c>
       <c r="D104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -7003,10 +6283,10 @@
         <v>2.955490613687514</v>
       </c>
       <c r="I104">
-        <v>5.210392163563169</v>
+        <v>5.208435154763756</v>
       </c>
       <c r="J104">
-        <v>-2.254901549875655</v>
+        <v>-2.252944541076242</v>
       </c>
     </row>
     <row r="105">
@@ -7026,15 +6306,12 @@
         </is>
       </c>
       <c r="D105">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F105">
-        <v>0.974708290490896</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G105">
         <v>26</v>
@@ -7043,10 +6320,10 @@
         <v>2.917855439851379</v>
       </c>
       <c r="I105">
-        <v>4.508922552087076</v>
+        <v>2.917855439851379</v>
       </c>
       <c r="J105">
-        <v>-1.591067112235697</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -7066,7 +6343,7 @@
         </is>
       </c>
       <c r="D106">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -7083,10 +6360,10 @@
         <v>2.866313560066672</v>
       </c>
       <c r="I106">
-        <v>1.033966800627679</v>
+        <v>1.032439410990276</v>
       </c>
       <c r="J106">
-        <v>1.832346759438993</v>
+        <v>1.833874149076395</v>
       </c>
     </row>
     <row r="107">
@@ -7106,15 +6383,12 @@
         </is>
       </c>
       <c r="D107">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F107">
-        <v>0.9711344995987063</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G107">
         <v>26</v>
@@ -7123,10 +6397,10 @@
         <v>2.797560411913858</v>
       </c>
       <c r="I107">
-        <v>2.70930695170997</v>
+        <v>2.797560411913858</v>
       </c>
       <c r="J107">
-        <v>0.08825346020388869</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -7266,7 +6540,7 @@
         </is>
       </c>
       <c r="D111">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -7306,7 +6580,7 @@
         </is>
       </c>
       <c r="D112">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -7323,10 +6597,10 @@
         <v>2.598570528143351</v>
       </c>
       <c r="I112">
-        <v>2.125053645156248</v>
+        <v>2.127041471635836</v>
       </c>
       <c r="J112">
-        <v>0.473516882987103</v>
+        <v>0.471529056507515</v>
       </c>
     </row>
     <row r="113">
@@ -7346,7 +6620,7 @@
         </is>
       </c>
       <c r="D113">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -7363,10 +6637,10 @@
         <v>2.596228133172809</v>
       </c>
       <c r="I113">
-        <v>2.713798233504921</v>
+        <v>2.769850165232657</v>
       </c>
       <c r="J113">
-        <v>-0.1175701003321121</v>
+        <v>-0.1736220320598485</v>
       </c>
     </row>
     <row r="114">
@@ -7386,11 +6660,11 @@
         </is>
       </c>
       <c r="D114">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>BASE_fallback</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="G114">
@@ -7423,7 +6697,7 @@
         </is>
       </c>
       <c r="D115">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -7463,7 +6737,7 @@
         </is>
       </c>
       <c r="D116">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -7480,10 +6754,10 @@
         <v>2.302435433265153</v>
       </c>
       <c r="I116">
-        <v>3.446086730237684</v>
+        <v>3.400944298567574</v>
       </c>
       <c r="J116">
-        <v>-1.143651296972531</v>
+        <v>-1.098508865302421</v>
       </c>
     </row>
     <row r="117">
@@ -7543,7 +6817,7 @@
         </is>
       </c>
       <c r="D118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -7560,10 +6834,10 @@
         <v>2.235174413347099</v>
       </c>
       <c r="I118">
-        <v>2.045195585460225</v>
+        <v>2.066714232633141</v>
       </c>
       <c r="J118">
-        <v>0.1899788278868741</v>
+        <v>0.1684601807139581</v>
       </c>
     </row>
     <row r="119">
@@ -7623,7 +6897,7 @@
         </is>
       </c>
       <c r="D120">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -7663,7 +6937,7 @@
         </is>
       </c>
       <c r="D121">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -7743,7 +7017,7 @@
         </is>
       </c>
       <c r="D123">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -7760,10 +7034,10 @@
         <v>1.976621956408089</v>
       </c>
       <c r="I123">
-        <v>1.724030260569778</v>
+        <v>1.724581492020042</v>
       </c>
       <c r="J123">
-        <v>0.2525916958383116</v>
+        <v>0.2520404643880478</v>
       </c>
     </row>
     <row r="124">
@@ -7783,7 +7057,7 @@
         </is>
       </c>
       <c r="D124">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -7823,7 +7097,7 @@
         </is>
       </c>
       <c r="D125">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -7863,7 +7137,7 @@
         </is>
       </c>
       <c r="D126">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -7880,10 +7154,10 @@
         <v>1.926173323346679</v>
       </c>
       <c r="I126">
-        <v>1.916843239561811</v>
+        <v>1.925082952432055</v>
       </c>
       <c r="J126">
-        <v>0.009330083784868437</v>
+        <v>0.001090370914623939</v>
       </c>
     </row>
     <row r="127">
@@ -7903,7 +7177,7 @@
         </is>
       </c>
       <c r="D127">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -7920,10 +7194,10 @@
         <v>1.898839688453783</v>
       </c>
       <c r="I127">
-        <v>1.6819483385728</v>
+        <v>1.684310214918519</v>
       </c>
       <c r="J127">
-        <v>0.2168913498809835</v>
+        <v>0.2145294735352641</v>
       </c>
     </row>
     <row r="128">
@@ -7943,7 +7217,7 @@
         </is>
       </c>
       <c r="D128">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -7960,10 +7234,10 @@
         <v>1.895328362172866</v>
       </c>
       <c r="I128">
-        <v>2.062016862886739</v>
+        <v>2.046847830536319</v>
       </c>
       <c r="J128">
-        <v>-0.166688500713873</v>
+        <v>-0.1515194683634531</v>
       </c>
     </row>
     <row r="129">
@@ -8023,7 +7297,7 @@
         </is>
       </c>
       <c r="D130">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -8080,10 +7354,10 @@
         <v>1.721311573236661</v>
       </c>
       <c r="I131">
-        <v>3.716146043457246</v>
+        <v>3.702735784762129</v>
       </c>
       <c r="J131">
-        <v>-1.994834470220584</v>
+        <v>-1.981424211525468</v>
       </c>
     </row>
     <row r="132">
@@ -8103,7 +7377,7 @@
         </is>
       </c>
       <c r="D132">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -8120,10 +7394,10 @@
         <v>1.649998610459949</v>
       </c>
       <c r="I132">
-        <v>1.629623107170037</v>
+        <v>1.649997637713811</v>
       </c>
       <c r="J132">
-        <v>0.02037550328991222</v>
+        <v>9.727461376396462E-07</v>
       </c>
     </row>
     <row r="133">
@@ -8223,7 +7497,7 @@
         </is>
       </c>
       <c r="D135">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -8240,10 +7514,10 @@
         <v>1.503019272288606</v>
       </c>
       <c r="I135">
-        <v>1.195125928330696</v>
+        <v>1.247339096330093</v>
       </c>
       <c r="J135">
-        <v>0.3078933439579092</v>
+        <v>0.2556801759585121</v>
       </c>
     </row>
     <row r="136">
@@ -8263,7 +7537,7 @@
         </is>
       </c>
       <c r="D136">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -8303,7 +7577,7 @@
         </is>
       </c>
       <c r="D137">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -8320,10 +7594,10 @@
         <v>1.402327856867523</v>
       </c>
       <c r="I137">
-        <v>2.008208803943539</v>
+        <v>1.775573135036843</v>
       </c>
       <c r="J137">
-        <v>-0.6058809470760158</v>
+        <v>-0.3732452781693205</v>
       </c>
     </row>
     <row r="138">
@@ -8343,7 +7617,7 @@
         </is>
       </c>
       <c r="D138">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -8360,10 +7634,10 @@
         <v>1.344183438100925</v>
       </c>
       <c r="I138">
-        <v>1.629045813768756</v>
+        <v>1.578442577117789</v>
       </c>
       <c r="J138">
-        <v>-0.2848623756678306</v>
+        <v>-0.2342591390168642</v>
       </c>
     </row>
     <row r="139">
@@ -8383,7 +7657,7 @@
         </is>
       </c>
       <c r="D139">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -8423,7 +7697,7 @@
         </is>
       </c>
       <c r="D140">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -8503,7 +7777,7 @@
         </is>
       </c>
       <c r="D142">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -8583,15 +7857,12 @@
         </is>
       </c>
       <c r="D144">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F144">
-        <v>0.896757999986041</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G144">
         <v>26</v>
@@ -8600,10 +7871,10 @@
         <v>1.2258078040987</v>
       </c>
       <c r="I144">
-        <v>1.267438136483056</v>
+        <v>1.2258078040987</v>
       </c>
       <c r="J144">
-        <v>-0.04163033238435609</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -8623,15 +7894,12 @@
         </is>
       </c>
       <c r="D145">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F145">
-        <v>0.9978026589514768</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G145">
         <v>26</v>
@@ -8640,10 +7908,10 @@
         <v>1.20223193421102</v>
       </c>
       <c r="I145">
-        <v>0.9861434325539906</v>
+        <v>1.20223193421102</v>
       </c>
       <c r="J145">
-        <v>0.2160885016570291</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -8663,7 +7931,7 @@
         </is>
       </c>
       <c r="D146">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -8680,10 +7948,10 @@
         <v>1.183150550856713</v>
       </c>
       <c r="I146">
-        <v>0.7642873945441496</v>
+        <v>0.7663196286606655</v>
       </c>
       <c r="J146">
-        <v>0.4188631563125634</v>
+        <v>0.4168309221960476</v>
       </c>
     </row>
     <row r="147">
@@ -8703,15 +7971,12 @@
         </is>
       </c>
       <c r="D147">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F147">
-        <v>0.9975718326013238</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G147">
         <v>26</v>
@@ -8720,10 +7985,10 @@
         <v>1.177400789719668</v>
       </c>
       <c r="I147">
-        <v>1.276659985655355</v>
+        <v>1.177400789719668</v>
       </c>
       <c r="J147">
-        <v>-0.09925919593568744</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -8743,15 +8008,12 @@
         </is>
       </c>
       <c r="D148">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F148">
-        <v>0.8901396713866181</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G148">
         <v>26</v>
@@ -8760,10 +8022,10 @@
         <v>1.14775624183832</v>
       </c>
       <c r="I148">
-        <v>0.860120501333469</v>
+        <v>1.14775624183832</v>
       </c>
       <c r="J148">
-        <v>0.2876357405048513</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -8783,15 +8045,12 @@
         </is>
       </c>
       <c r="D149">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F149">
-        <v>0.980532873622632</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G149">
         <v>26</v>
@@ -8800,10 +8059,10 @@
         <v>1.143935627624398</v>
       </c>
       <c r="I149">
-        <v>1.119997753042155</v>
+        <v>1.143935627624398</v>
       </c>
       <c r="J149">
-        <v>0.02393787458224272</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -8823,7 +8082,7 @@
         </is>
       </c>
       <c r="D150">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -8840,10 +8099,10 @@
         <v>1.137735805837282</v>
       </c>
       <c r="I150">
-        <v>0.7899090711271493</v>
+        <v>0.7911174444771417</v>
       </c>
       <c r="J150">
-        <v>0.3478267347101325</v>
+        <v>0.34661836136014</v>
       </c>
     </row>
     <row r="151">
@@ -8863,15 +8122,12 @@
         </is>
       </c>
       <c r="D151">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F151">
-        <v>0.8822594849608131</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G151">
         <v>26</v>
@@ -8880,10 +8136,10 @@
         <v>1.124079035672742</v>
       </c>
       <c r="I151">
-        <v>5.625894420495276</v>
+        <v>1.124079035672742</v>
       </c>
       <c r="J151">
-        <v>-4.501815384822534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -8903,15 +8159,12 @@
         </is>
       </c>
       <c r="D152">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F152">
-        <v>0.9954459170872036</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G152">
         <v>26</v>
@@ -8920,10 +8173,10 @@
         <v>1.11061377725523</v>
       </c>
       <c r="I152">
-        <v>1.097109283904496</v>
+        <v>1.11061377725523</v>
       </c>
       <c r="J152">
-        <v>0.01350449335073356</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -8943,7 +8196,7 @@
         </is>
       </c>
       <c r="D153">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -9023,15 +8276,12 @@
         </is>
       </c>
       <c r="D155">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F155">
-        <v>0.950809002809078</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G155">
         <v>26</v>
@@ -9040,10 +8290,10 @@
         <v>1.058950088101158</v>
       </c>
       <c r="I155">
-        <v>1.216017740591384</v>
+        <v>1.058950088101158</v>
       </c>
       <c r="J155">
-        <v>-0.1570676524902259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -9120,10 +8370,10 @@
         <v>0.9761688117668174</v>
       </c>
       <c r="I157">
-        <v>0.7312875372353178</v>
+        <v>0.8254147529556495</v>
       </c>
       <c r="J157">
-        <v>0.2448812745314995</v>
+        <v>0.1507540588111679</v>
       </c>
     </row>
     <row r="158">
@@ -9143,15 +8393,12 @@
         </is>
       </c>
       <c r="D158">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F158">
-        <v>0.9800393525483831</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G158">
         <v>26</v>
@@ -9160,10 +8407,10 @@
         <v>0.9741925240815006</v>
       </c>
       <c r="I158">
-        <v>0.6676937409318225</v>
+        <v>0.9741925240815006</v>
       </c>
       <c r="J158">
-        <v>0.306498783149678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -9183,7 +8430,7 @@
         </is>
       </c>
       <c r="D159">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -9200,10 +8447,10 @@
         <v>0.9675322740524357</v>
       </c>
       <c r="I159">
-        <v>1.049263096096612</v>
+        <v>1.037210147336593</v>
       </c>
       <c r="J159">
-        <v>-0.08173082204417592</v>
+        <v>-0.06967787328415698</v>
       </c>
     </row>
     <row r="160">
@@ -9223,7 +8470,7 @@
         </is>
       </c>
       <c r="D160">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -9240,10 +8487,10 @@
         <v>0.94207759660138</v>
       </c>
       <c r="I160">
-        <v>2.598629050752063</v>
+        <v>2.596792491318175</v>
       </c>
       <c r="J160">
-        <v>-1.656551454150683</v>
+        <v>-1.654714894716795</v>
       </c>
     </row>
     <row r="161">
@@ -9263,7 +8510,7 @@
         </is>
       </c>
       <c r="D161">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -9280,10 +8527,10 @@
         <v>0.9369459990017591</v>
       </c>
       <c r="I161">
-        <v>4.361734845231355</v>
+        <v>4.345054350249501</v>
       </c>
       <c r="J161">
-        <v>-3.424788846229596</v>
+        <v>-3.408108351247741</v>
       </c>
     </row>
     <row r="162">
@@ -9303,11 +8550,11 @@
         </is>
       </c>
       <c r="D162">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>BASE_fallback</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="G162">
@@ -9340,7 +8587,7 @@
         </is>
       </c>
       <c r="D163">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -9357,10 +8604,10 @@
         <v>0.922677844731381</v>
       </c>
       <c r="I163">
-        <v>1.028909642561798</v>
+        <v>1.022285483630878</v>
       </c>
       <c r="J163">
-        <v>-0.106231797830417</v>
+        <v>-0.09960763889949664</v>
       </c>
     </row>
     <row r="164">
@@ -9380,15 +8627,12 @@
         </is>
       </c>
       <c r="D164">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F164">
-        <v>0.961572579017993</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G164">
         <v>26</v>
@@ -9397,10 +8641,10 @@
         <v>0.9208710082916296</v>
       </c>
       <c r="I164">
-        <v>1.470940354702885</v>
+        <v>0.9208710082916296</v>
       </c>
       <c r="J164">
-        <v>-0.5500693464112556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -9420,15 +8664,12 @@
         </is>
       </c>
       <c r="D165">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F165">
-        <v>0.998825871500844</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G165">
         <v>26</v>
@@ -9437,10 +8678,10 @@
         <v>0.9192066594472316</v>
       </c>
       <c r="I165">
-        <v>1.224444082412253</v>
+        <v>0.9192066594472316</v>
       </c>
       <c r="J165">
-        <v>-0.3052374229650211</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -9460,15 +8701,12 @@
         </is>
       </c>
       <c r="D166">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F166">
-        <v>0.9912033439380552</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G166">
         <v>26</v>
@@ -9477,10 +8715,10 @@
         <v>0.9079978927602861</v>
       </c>
       <c r="I166">
-        <v>1.085587892999091</v>
+        <v>0.9079978927602861</v>
       </c>
       <c r="J166">
-        <v>-0.1775900002388047</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -9500,15 +8738,12 @@
         </is>
       </c>
       <c r="D167">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F167">
-        <v>0.9799946402992936</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G167">
         <v>26</v>
@@ -9517,10 +8752,10 @@
         <v>0.8803468081208102</v>
       </c>
       <c r="I167">
-        <v>0.9978822957521633</v>
+        <v>0.8803468081208102</v>
       </c>
       <c r="J167">
-        <v>-0.117535487631353</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -9540,7 +8775,7 @@
         </is>
       </c>
       <c r="D168">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -9557,10 +8792,10 @@
         <v>0.8742464581852942</v>
       </c>
       <c r="I168">
-        <v>3.023033450312448</v>
+        <v>3.014010957725795</v>
       </c>
       <c r="J168">
-        <v>-2.148786992127153</v>
+        <v>-2.139764499540501</v>
       </c>
     </row>
     <row r="169">
@@ -9580,7 +8815,7 @@
         </is>
       </c>
       <c r="D169">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -9597,10 +8832,10 @@
         <v>0.8722133462137347</v>
       </c>
       <c r="I169">
-        <v>0.6716438009094745</v>
+        <v>0.6740332685220185</v>
       </c>
       <c r="J169">
-        <v>0.2005695453042602</v>
+        <v>0.1981800776917162</v>
       </c>
     </row>
     <row r="170">
@@ -9660,7 +8895,7 @@
         </is>
       </c>
       <c r="D171">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -9677,10 +8912,10 @@
         <v>0.8244748552853306</v>
       </c>
       <c r="I171">
-        <v>1.07717115883062</v>
+        <v>1.085632972950154</v>
       </c>
       <c r="J171">
-        <v>-0.252696303545289</v>
+        <v>-0.2611581176648231</v>
       </c>
     </row>
     <row r="172">
@@ -9700,15 +8935,12 @@
         </is>
       </c>
       <c r="D172">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F172">
-        <v>0.9894959097869224</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G172">
         <v>26</v>
@@ -9717,10 +8949,10 @@
         <v>0.7654009651973397</v>
       </c>
       <c r="I172">
-        <v>0.5535647783812121</v>
+        <v>0.7654009651973397</v>
       </c>
       <c r="J172">
-        <v>0.2118361868161276</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -9740,15 +8972,12 @@
         </is>
       </c>
       <c r="D173">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F173">
-        <v>0.9768126498004104</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G173">
         <v>26</v>
@@ -9757,10 +8986,10 @@
         <v>0.753621738640046</v>
       </c>
       <c r="I173">
-        <v>0.9096451793824011</v>
+        <v>0.753621738640046</v>
       </c>
       <c r="J173">
-        <v>-0.1560234407423551</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -9797,10 +9026,10 @@
         <v>0.725684055953815</v>
       </c>
       <c r="I174">
-        <v>1.172060936326114</v>
+        <v>1.16824469781737</v>
       </c>
       <c r="J174">
-        <v>-0.4463768803722991</v>
+        <v>-0.4425606418635545</v>
       </c>
     </row>
     <row r="175">
@@ -9820,15 +9049,12 @@
         </is>
       </c>
       <c r="D175">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F175">
-        <v>0.9793304635475664</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G175">
         <v>26</v>
@@ -9837,10 +9063,10 @@
         <v>0.7044826393384088</v>
       </c>
       <c r="I175">
-        <v>0.698364734435567</v>
+        <v>0.7044826393384088</v>
       </c>
       <c r="J175">
-        <v>0.006117904902841809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -9860,15 +9086,12 @@
         </is>
       </c>
       <c r="D176">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F176">
-        <v>0.9978602117413538</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G176">
         <v>26</v>
@@ -9877,10 +9100,10 @@
         <v>0.6866602236940718</v>
       </c>
       <c r="I176">
-        <v>0.5677351265894207</v>
+        <v>0.6866602236940718</v>
       </c>
       <c r="J176">
-        <v>0.118925097104651</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -9900,15 +9123,12 @@
         </is>
       </c>
       <c r="D177">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F177">
-        <v>0.9873555598269006</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G177">
         <v>26</v>
@@ -9917,10 +9137,10 @@
         <v>0.6720484955002144</v>
       </c>
       <c r="I177">
-        <v>0.7292273174603386</v>
+        <v>0.6720484955002144</v>
       </c>
       <c r="J177">
-        <v>-0.05717882196012425</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -9940,15 +9160,12 @@
         </is>
       </c>
       <c r="D178">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F178">
-        <v>0.9941940856935556</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G178">
         <v>26</v>
@@ -9957,10 +9174,10 @@
         <v>0.6643472323989948</v>
       </c>
       <c r="I178">
-        <v>0.6264604665154013</v>
+        <v>0.6643472323989948</v>
       </c>
       <c r="J178">
-        <v>0.03788676588359352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -10020,7 +9237,7 @@
         </is>
       </c>
       <c r="D180">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -10037,10 +9254,10 @@
         <v>0.6072260481628153</v>
       </c>
       <c r="I180">
-        <v>0.5275201793938948</v>
+        <v>0.5292322633384873</v>
       </c>
       <c r="J180">
-        <v>0.0797058687689205</v>
+        <v>0.07799378482432806</v>
       </c>
     </row>
     <row r="181">
@@ -10260,15 +9477,12 @@
         </is>
       </c>
       <c r="D186">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F186">
-        <v>0.9529766090438704</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G186">
         <v>26</v>
@@ -10277,10 +9491,10 @@
         <v>0.4840547651189584</v>
       </c>
       <c r="I186">
-        <v>0.3297440349122036</v>
+        <v>0.4840547651189584</v>
       </c>
       <c r="J186">
-        <v>0.1543107302067548</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -10300,7 +9514,7 @@
         </is>
       </c>
       <c r="D187">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -10317,10 +9531,10 @@
         <v>0.4679397807046715</v>
       </c>
       <c r="I187">
-        <v>1.621699610319567</v>
+        <v>1.613641872364766</v>
       </c>
       <c r="J187">
-        <v>-1.153759829614896</v>
+        <v>-1.145702091660094</v>
       </c>
     </row>
     <row r="188">
@@ -10340,15 +9554,12 @@
         </is>
       </c>
       <c r="D188">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F188">
-        <v>0.9505231978860246</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G188">
         <v>26</v>
@@ -10357,10 +9568,10 @@
         <v>0.4624471378082669</v>
       </c>
       <c r="I188">
-        <v>0.5545948442417091</v>
+        <v>0.4624471378082669</v>
       </c>
       <c r="J188">
-        <v>-0.09214770643344222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -10380,15 +9591,12 @@
         </is>
       </c>
       <c r="D189">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F189">
-        <v>0.9991206080717208</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G189">
         <v>26</v>
@@ -10397,10 +9605,10 @@
         <v>0.4584436656208899</v>
       </c>
       <c r="I189">
-        <v>0.4091382643700465</v>
+        <v>0.4584436656208899</v>
       </c>
       <c r="J189">
-        <v>0.04930540125084337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -10437,10 +9645,10 @@
         <v>0.4565397092491535</v>
       </c>
       <c r="I190">
-        <v>0.5485564160746699</v>
+        <v>0.5319598080243914</v>
       </c>
       <c r="J190">
-        <v>-0.09201670682551638</v>
+        <v>-0.07542009877523786</v>
       </c>
     </row>
     <row r="191">
@@ -10460,15 +9668,12 @@
         </is>
       </c>
       <c r="D191">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F191">
-        <v>0.9985426189388515</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G191">
         <v>26</v>
@@ -10477,10 +9682,10 @@
         <v>0.4037085718694741</v>
       </c>
       <c r="I191">
-        <v>0.4000015875188488</v>
+        <v>0.4037085718694741</v>
       </c>
       <c r="J191">
-        <v>0.003706984350625275</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -10500,7 +9705,7 @@
         </is>
       </c>
       <c r="D192">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -10517,10 +9722,10 @@
         <v>0.3781312337402647</v>
       </c>
       <c r="I192">
-        <v>0.3701876359523618</v>
+        <v>0.3705305364440644</v>
       </c>
       <c r="J192">
-        <v>0.007943597787902934</v>
+        <v>0.007600697296200276</v>
       </c>
     </row>
     <row r="193">
@@ -10540,15 +9745,12 @@
         </is>
       </c>
       <c r="D193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F193">
-        <v>0.9201282790000826</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G193">
         <v>26</v>
@@ -10557,10 +9759,10 @@
         <v>0.350503076735108</v>
       </c>
       <c r="I193">
-        <v>0.9732302988303007</v>
+        <v>0.350503076735108</v>
       </c>
       <c r="J193">
-        <v>-0.6227272220951927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -10620,15 +9822,12 @@
         </is>
       </c>
       <c r="D195">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F195">
-        <v>0.9477114167624322</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G195">
         <v>26</v>
@@ -10637,10 +9836,10 @@
         <v>0.3479169387901151</v>
       </c>
       <c r="I195">
-        <v>0.2568028561318761</v>
+        <v>0.3479169387901151</v>
       </c>
       <c r="J195">
-        <v>0.09111408265823895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -10660,15 +9859,12 @@
         </is>
       </c>
       <c r="D196">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F196">
-        <v>0.951994281103229</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G196">
         <v>26</v>
@@ -10677,10 +9873,10 @@
         <v>0.3456593624237623</v>
       </c>
       <c r="I196">
-        <v>0.2506479808730535</v>
+        <v>0.3456593624237623</v>
       </c>
       <c r="J196">
-        <v>0.09501138155070882</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -10740,15 +9936,12 @@
         </is>
       </c>
       <c r="D198">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F198">
-        <v>0.9815595748490992</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G198">
         <v>26</v>
@@ -10757,10 +9950,10 @@
         <v>0.29050569988783</v>
       </c>
       <c r="I198">
-        <v>0.3577762606559016</v>
+        <v>0.29050569988783</v>
       </c>
       <c r="J198">
-        <v>-0.06727056076807159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -10780,15 +9973,12 @@
         </is>
       </c>
       <c r="D199">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F199">
-        <v>0.9440838220529262</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G199">
         <v>26</v>
@@ -10797,10 +9987,10 @@
         <v>0.2885212620083857</v>
       </c>
       <c r="I199">
-        <v>0.4350147938737887</v>
+        <v>0.2885212620083857</v>
       </c>
       <c r="J199">
-        <v>-0.146493531865403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -10820,15 +10010,12 @@
         </is>
       </c>
       <c r="D200">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F200">
-        <v>0.9967494569512459</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G200">
         <v>26</v>
@@ -10837,10 +10024,10 @@
         <v>0.2860788845163144</v>
       </c>
       <c r="I200">
-        <v>0.2824642167447321</v>
+        <v>0.2860788845163144</v>
       </c>
       <c r="J200">
-        <v>0.003614667771582314</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -10860,15 +10047,12 @@
         </is>
       </c>
       <c r="D201">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F201">
-        <v>0.8208676434348308</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G201">
         <v>26</v>
@@ -10877,10 +10061,10 @@
         <v>0.276703631696305</v>
       </c>
       <c r="I201">
-        <v>1.888236746589256</v>
+        <v>0.276703631696305</v>
       </c>
       <c r="J201">
-        <v>-1.611533114892951</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -10900,15 +10084,12 @@
         </is>
       </c>
       <c r="D202">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F202">
-        <v>0.9872226029389914</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G202">
         <v>26</v>
@@ -10917,10 +10098,10 @@
         <v>0.2749869961545904</v>
       </c>
       <c r="I202">
-        <v>0.5083430916941852</v>
+        <v>0.2749869961545904</v>
       </c>
       <c r="J202">
-        <v>-0.2333560955395949</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -10940,15 +10121,12 @@
         </is>
       </c>
       <c r="D203">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F203">
-        <v>0.9799932810192457</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G203">
         <v>26</v>
@@ -10957,10 +10135,10 @@
         <v>0.2547803519917533</v>
       </c>
       <c r="I203">
-        <v>0.2542187727406757</v>
+        <v>0.2547803519917533</v>
       </c>
       <c r="J203">
-        <v>0.0005615792510776374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -10980,7 +10158,7 @@
         </is>
       </c>
       <c r="D204">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -10997,10 +10175,10 @@
         <v>0.2107399172609231</v>
       </c>
       <c r="I204">
-        <v>0.3796634500315353</v>
+        <v>0.377934371460905</v>
       </c>
       <c r="J204">
-        <v>-0.1689235327706122</v>
+        <v>-0.167194454199982</v>
       </c>
     </row>
     <row r="205">
@@ -11020,15 +10198,12 @@
         </is>
       </c>
       <c r="D205">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>D_city</t>
-        </is>
-      </c>
-      <c r="F205">
-        <v>0.9886035180040984</v>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="G205">
         <v>26</v>
@@ -11037,10 +10212,10 @@
         <v>0.2069985928760783</v>
       </c>
       <c r="I205">
-        <v>0.2064170206541731</v>
+        <v>0.2069985928760783</v>
       </c>
       <c r="J205">
-        <v>0.0005815722219051356</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -11060,7 +10235,7 @@
         </is>
       </c>
       <c r="D206">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -11077,10 +10252,10 @@
         <v>0.1521099946939301</v>
       </c>
       <c r="I206">
-        <v>0.9364919031625417</v>
+        <v>0.9317019990636625</v>
       </c>
       <c r="J206">
-        <v>-0.7843819084686117</v>
+        <v>-0.7795920043697324</v>
       </c>
     </row>
   </sheetData>
